--- a/human_validation/judge/kor/judge_D008_S002_P001__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D008_S002_P001__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -559,12 +556,439 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 이번 역사협회 모금 행사에서 제가 너무 많은 일을 떠맡은 것 같아서 왔어요. 마치 혼자서 이 모든 걸 다 해낼 수 있는 것처럼 행동했거든요—퀼트 디자인 시작하고, 자원봉사자들한테 전화 돌리고, 일정 짜고, 마감일 약속하고요—근데 지금 보니까 도저히 그걸 다 감당할 수 없다는 게 확실해졌어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 당장 할 수 있는 게 없는 순간에도 이 모금 행사에 대해 계속 걱정하셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 잘 모르겠어요. 뭔가 떠올리게 하는 게 있으면 생각하긴 했는데, 할 수 있는 게 없는데도 끊임없이 걱정만 했는지는 모르겠어요. 그보다는 그냥 일이 제가 감당할 수 있는 수준보다 커져버린 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 모금 행사를 제대로 감당하지 못한 것에 대해 스스로를 심하게 몰아붙이고 계신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 스스로한테 꽤 심하게 굴고 있어요. 밀린 주문 하나하나, 자원봉사자들한테 날카롭게 말했던 순간들을 계속 떠올리는데, 그냥 이런 생각이 들어요... 교회도, 역사협회도, 사실상 마을 전체를 실망시켰다는.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 다른 것에 집중하려고 해도 모금 행사와 관련된 같은 생각이나 충동이 반복적으로 떠오르시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 그걸 반복되는 충동이라고 부를 수 있을지는 모르겠어요. 생각은 하죠, 특히 못 끝낸 게 뭔가 떠오를 때는요. 근데 다른 것에 집중하려고 할 때 그게 제 머릿속을 완전히 장악하는 건 딱히 못 느꼈어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 모금 행사에 대해 생각하시는 게 원해서 그러시는 건가요, 아니면 생각을 멈출 수가 없어서 그러시는 건가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 딱히 앉아서 그것만 생각하고 싶어서 그러는 건 아닌 것 같은데, 그렇다고 멈출 수가 없는 느낌이라고도 못 하겠어요. 그냥 뭔가 떠올리게 하는 게 있으면 생각이 나고, 그러면 한동안 기분이 안 좋아져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 원하지 않는데도 모금 행사에 대한 생각이 드는 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 가끔은요, 근데 머릿속에 딱 박혀버린 느낌은 아니에요. 관련된 뭔가를 보면 문득 떠오르고, 생각하고 싶지 않은데 하고 있다 싶긴 한데, 보통 조금 지나면 지나가요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 원하지 않는데도 모금 행사에 대한 생각이 저절로 떠오르는 느낌이 드신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 생각할 계획이 없었는데도 떠오르긴 하는데, 보통은 뭔가 계기가 있어요. 그냥 아무 이유 없이 떠오른다고까지는 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 모금 행사에 대한 생각을 스스로 통제할 수 없다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 통제할 수 없다고까지는 말 못 하겠어요. 떠오르면 싫긴 한데, 보통 조금 있으면 다른 데로 생각을 돌릴 수 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 잠들려고 하거나 쉬려고 할 때도 모금 행사 생각이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 네. 수면에도 좀 영향을 주고 있어요. 한동안은 몇 시간밖에 못 자는데도 당장 바느질을 시작하거나 전화를 돌릴 준비가 된 것처럼 깨곤 했어요. 요즘은 그보다는 누워서 걱정만 하거나, 늦게까지 자도 여전히 지친 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 모금 행사에 대한 생각이 억지로 머릿속에 밀고 들어오는 느낌이 드신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 밀고 들어온다고까지는 말 못 하겠어요. 특히 이미 스트레스를 받고 있을 때 가끔 떠오르긴 하는데, 정확히 제 마음을 장악하는 느낌은 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 모금 행사에 대해 원치 않고 괴로운, 침투적인 생각을 하고 계신다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 정확히 침투적이라고 부를 수 있을지는 모르겠어요. 원치 않고 가끔 속상한 건 맞는데, 떨쳐낼 수 없는 괴로운 생각이라기보다는 계속 돌아오는 걱정에 더 가까운 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 모금 행사에 대해 생각하지 않을 때도 대부분의 시간 동안 불안하신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 잘 모르겠어요. 요즘 초조한 느낌이 많이 들긴 하는데, 모금 행사 생각을 안 할 때도 그런지는 딱히 신경 써서 본 적이 없어요. 좀 더 생각해 봐야 할 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 모금 행사나 그와 관련된 것을 전혀 생각하지 않을 때도 불안하신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 잘 모르겠어요. 그렇게 따로 구분해서 생각해 본 적이 없어요. 긴장된다는 건 많이 느끼는데, 모금 행사나 관련된 걸 안 떠올릴 때도 그런지는... 좀 더 신경 써서 봐야 할 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 즐거운 일을 하고 있고 모금 행사 생각이 안 날 때도 불안하신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 잘 모르겠어요. 진짜로 즐거운 일에 몰두해 있을 때는 별로 못 느끼는 것 같긴 한데, 모금 행사 생각이 완전히 사라졌을 때도 불안이 여전히 있는지는 자세히 신경 써서 보지는 않았어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 즐거운 일을 하고 계실 때, 모금 행사 생각을 안 하고 있어도 불안하신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 잘 모르겠어요. 즐거운 일을 하고 있을 때는 딴 데 정신이 팔려서 잘 못 느끼는 것 같아요. 그게 여전히 있는지 없는지는 확실히 말씀드리기 어려워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 아무것도 하지 않고 특별히 아무 생각도 하지 않을 때도 불안하신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 잘 모르겠어요. 아무 일도 없을 때 제가 뭘 느끼는지 앉아서 확인해 보는 편이 아니라서요. 가끔 긴장되는 건 아는데, 특별히 아무 생각도 안 할 때도 그런지는... 딱히 눈치채지 못했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 아무것도 하지 않고 특별히 아무 생각도 하지 않을 때 불안하신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 잘 모르겠어요. 정확히 그런 상황에 대해서는 충분히 신경 써서 본 적이 없어요. 그냥 아무 일 없이 앉아 있을 때 가끔 약간 불편한 느낌이 들 수는 있는데, 그게 불안인지, 아무 생각도 안 할 때 일어나는 건지 확실히는 모르겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 아무것도 하지 않고, 모금 행사도, 다른 특별한 것도 생각하지 않을 때 불안하신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 솔직히 잘 모르겠어요. 아무것도 안 하고 모금 행사 생각도 안 할 때, 그 순간에 제가 뭘 느끼는지 잘 모르겠어요. 예 아니오라고 분명하게 말할 정도로 눈치채지는 못했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 아무 생각도 전혀 하지 않을 때 불안하신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 확실히 말씀드리기 어려워요. 머릿속이 완전히 비어 있을 때 불안을 느낀 적은 딱히 없는 것 같아요. 그런 정확한 상황에서는 저도 판단하기가 힘들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사 질문] 아무 생각도 안 하고 불안할 특별한 이유도 없을 때 불안하신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 환자 응답] 잘 모르겠어요. 이유도 없고 아무 생각도 안 할 때 불안이 올라오는 걸 딱히 눈치챈 적은 없는 것 같아요. 만약 그런 일이 있다 해도, 그렇게는 인식하지 못했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>진단명: 제1형 양극성장애 (D008)
 인구통계: 성별 여성 / 나이 59 / 직업상태 not in workforce / 최종학력 대학 재학
@@ -573,497 +997,46 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S040
-배경 서술: 도미니크가 집에서 운영하던 퀼트 공방은 그녀가 대회에서 우승한 뒤 지역 역사협회가 모금 행사를 위한 전통 테마 작품들을 대량으로 제작해 달라고 요청하고 행사에서 더 큰 리더십 역할을 맡아달라고 하면서 갑작스럽게 달라졌다. 이후 5개월에 걸쳐 그 흥분과 부담감은 유난히 고양되고 예민한 추진력이 두드러지는 뚜렷한 시기로 발전했다. 그녀는 잠을 훨씬 적게 잤고, 기획 회의에서 빠르게 말을 쏟아냈으며, 비현실적인 마감 기한을 약속했고, 협회를 위한 자신의 아이디어들이 분명히 마을을 변화시킬 것처럼 대했다. 주문이 밀리고 자원봉사자들과 갈등이 생기자 그녀는 오랜 우울 국면으로 접어들어, 텃밭과 퀼트 출품작 관리를 그만두고, 교회와 지역사회를 실망시켰다는 죄책감에 사로잡혔으며, 반복적으로 죽음에 대한 생각을 하기 시작했다. 그녀가 집안일이나 협회에서의 의무를 감당하지 못하게 되자 남편이 먼저 주치의에게 연락했고, 그녀는 정신건강의학과 평가를 위해 의뢰되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 이번 역사협회 모금 행사에서 제가 너무 많은 일을 떠맡은 것 같아서 왔어요. 마치 혼자서 이 모든 걸 다 해낼 수 있는 것처럼 행동했거든요—퀼트 디자인 시작하고, 자원봉사자들한테 전화 돌리고, 일정 짜고, 마감일 약속하고요—근데 지금 보니까 도저히 그걸 다 감당할 수 없다는 게 확실해졌어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 당장 할 수 있는 게 없는 순간에도 이 모금 행사에 대해 계속 걱정하셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 잘 모르겠어요. 뭔가 떠올리게 하는 게 있으면 생각하긴 했는데, 할 수 있는 게 없는데도 끊임없이 걱정만 했는지는 모르겠어요. 그보다는 그냥 일이 제가 감당할 수 있는 수준보다 커져버린 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 모금 행사를 제대로 감당하지 못한 것에 대해 스스로를 심하게 몰아붙이고 계신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 스스로한테 꽤 심하게 굴고 있어요. 밀린 주문 하나하나, 자원봉사자들한테 날카롭게 말했던 순간들을 계속 떠올리는데, 그냥 이런 생각이 들어요... 교회도, 역사협회도, 사실상 마을 전체를 실망시켰다는.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 다른 것에 집중하려고 해도 모금 행사와 관련된 같은 생각이나 충동이 반복적으로 떠오르시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 그걸 반복되는 충동이라고 부를 수 있을지는 모르겠어요. 생각은 하죠, 특히 못 끝낸 게 뭔가 떠오를 때는요. 근데 다른 것에 집중하려고 할 때 그게 제 머릿속을 완전히 장악하는 건 딱히 못 느꼈어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 모금 행사에 대해 생각하시는 게 원해서 그러시는 건가요, 아니면 생각을 멈출 수가 없어서 그러시는 건가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 딱히 앉아서 그것만 생각하고 싶어서 그러는 건 아닌 것 같은데, 그렇다고 멈출 수가 없는 느낌이라고도 못 하겠어요. 그냥 뭔가 떠올리게 하는 게 있으면 생각이 나고, 그러면 한동안 기분이 안 좋아져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 원하지 않는데도 모금 행사에 대한 생각이 드는 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 가끔은요, 근데 머릿속에 딱 박혀버린 느낌은 아니에요. 관련된 뭔가를 보면 문득 떠오르고, 생각하고 싶지 않은데 하고 있다 싶긴 한데, 보통 조금 지나면 지나가요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 원하지 않는데도 모금 행사에 대한 생각이 저절로 떠오르는 느낌이 드신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 생각할 계획이 없었는데도 떠오르긴 하는데, 보통은 뭔가 계기가 있어요. 그냥 아무 이유 없이 떠오른다고까지는 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 모금 행사에 대한 생각을 스스로 통제할 수 없다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 통제할 수 없다고까지는 말 못 하겠어요. 떠오르면 싫긴 한데, 보통 조금 있으면 다른 데로 생각을 돌릴 수 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 잠들려고 하거나 쉬려고 할 때도 모금 행사 생각이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 네. 수면에도 좀 영향을 주고 있어요. 한동안은 몇 시간밖에 못 자는데도 당장 바느질을 시작하거나 전화를 돌릴 준비가 된 것처럼 깨곤 했어요. 요즘은 그보다는 누워서 걱정만 하거나, 늦게까지 자도 여전히 지친 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 모금 행사에 대한 생각이 억지로 머릿속에 밀고 들어오는 느낌이 드신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 밀고 들어온다고까지는 말 못 하겠어요. 특히 이미 스트레스를 받고 있을 때 가끔 떠오르긴 하는데, 정확히 제 마음을 장악하는 느낌은 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 모금 행사에 대해 원치 않고 괴로운, 침투적인 생각을 하고 계신다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 정확히 침투적이라고 부를 수 있을지는 모르겠어요. 원치 않고 가끔 속상한 건 맞는데, 떨쳐낼 수 없는 괴로운 생각이라기보다는 계속 돌아오는 걱정에 더 가까운 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 모금 행사에 대해 생각하지 않을 때도 대부분의 시간 동안 불안하신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 잘 모르겠어요. 요즘 초조한 느낌이 많이 들긴 하는데, 모금 행사 생각을 안 할 때도 그런지는 딱히 신경 써서 본 적이 없어요. 좀 더 생각해 봐야 할 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 모금 행사나 그와 관련된 것을 전혀 생각하지 않을 때도 불안하신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 잘 모르겠어요. 그렇게 따로 구분해서 생각해 본 적이 없어요. 긴장된다는 건 많이 느끼는데, 모금 행사나 관련된 걸 안 떠올릴 때도 그런지는... 좀 더 신경 써서 봐야 할 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 즐거운 일을 하고 있고 모금 행사 생각이 안 날 때도 불안하신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 잘 모르겠어요. 진짜로 즐거운 일에 몰두해 있을 때는 별로 못 느끼는 것 같긴 한데, 모금 행사 생각이 완전히 사라졌을 때도 불안이 여전히 있는지는 자세히 신경 써서 보지는 않았어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 즐거운 일을 하고 계실 때, 모금 행사 생각을 안 하고 있어도 불안하신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 잘 모르겠어요. 즐거운 일을 하고 있을 때는 딴 데 정신이 팔려서 잘 못 느끼는 것 같아요. 그게 여전히 있는지 없는지는 확실히 말씀드리기 어려워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 아무것도 하지 않고 특별히 아무 생각도 하지 않을 때도 불안하신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 잘 모르겠어요. 아무 일도 없을 때 제가 뭘 느끼는지 앉아서 확인해 보는 편이 아니라서요. 가끔 긴장되는 건 아는데, 특별히 아무 생각도 안 할 때도 그런지는... 딱히 눈치채지 못했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 아무것도 하지 않고 특별히 아무 생각도 하지 않을 때 불안하신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 잘 모르겠어요. 정확히 그런 상황에 대해서는 충분히 신경 써서 본 적이 없어요. 그냥 아무 일 없이 앉아 있을 때 가끔 약간 불편한 느낌이 들 수는 있는데, 그게 불안인지, 아무 생각도 안 할 때 일어나는 건지 확실히는 모르겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 아무것도 하지 않고, 모금 행사도, 다른 특별한 것도 생각하지 않을 때 불안하신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 솔직히 잘 모르겠어요. 아무것도 안 하고 모금 행사 생각도 안 할 때, 그 순간에 제가 뭘 느끼는지 잘 모르겠어요. 예 아니오라고 분명하게 말할 정도로 눈치채지는 못했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 아무 생각도 전혀 하지 않을 때 불안하신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 확실히 말씀드리기 어려워요. 머릿속이 완전히 비어 있을 때 불안을 느낀 적은 딱히 없는 것 같아요. 그런 정확한 상황에서는 저도 판단하기가 힘들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 의사 질문] 아무 생각도 안 하고 불안할 특별한 이유도 없을 때 불안하신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 환자 응답] 잘 모르겠어요. 이유도 없고 아무 생각도 안 할 때 불안이 올라오는 걸 딱히 눈치챈 적은 없는 것 같아요. 만약 그런 일이 있다 해도, 그렇게는 인식하지 못했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+배경 서술: 도미니크가 집에서 운영하던 퀼트 공방은 그녀가 대회에서 우승한 뒤 지역 역사협회가 모금 행사를 위한 전통 테마 작품들을 대량으로 제작해 달라고 요청하고 행사에서 더 큰 리더십 역할을 맡아달라고 하면서 갑작스럽게 달라졌다. 이후 5개월에 걸쳐 그 흥분과 부담감은 유난히 고양되고 예민한 추진력이 두드러지는 뚜렷한 시기로 발전했다. 그녀는 잠을 훨씬 적게 잤고, 기획 회의에서 빠르게 말을 쏟아냈으며, 비현실적인 마감 기한을 약속했고, 협회를 위한 자신의 아이디어들이 분명히 마을을 변화시킬 것처럼 대했다. 주문이 밀리고 자원봉사자들과 갈등이 생기자 그녀는 오랜 우울 국면으로 접어들어, 텃밭과 퀼트 출품작 관리를 그만두고, 교회와 지역사회를 실망시켰다는 죄책감에 사로잡혔으며, 반복적으로 죽음에 대한 생각을 하기 시작했다. 그녀가 집안일이나 협회에서의 의무를 감당하지 못하게 되자 남편이 먼저 주치의에게 연락했고, 그녀는 정신건강의학과 평가를 위해 의뢰되었다.
+표집된 증상 목록:
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S028 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
+  - S033 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+  - S034 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - S035 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).
+  - S037 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.
+  - S038 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.
+  - S040 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>[20번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 범불안장애 (D011); 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: None (None, ICD: F48.8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=3, 커버리지=0.6)
-  확인된 근거: 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).; 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.; 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.
-  누락: 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.; 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.; 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).; 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.; 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.; 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=3, 커버리지=0.6)
-  확인된 근거: 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
-  누락: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
+          <t>의사의 최종 진단: None (None, ICD: F48.8)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=3, 커버리지=0.6)
+확인된 근거:
+  - 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).
+  - 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.
+  - 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.
+체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=3, 커버리지=0.6)
+확인된 근거:
+  - 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D008_S002_P001__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D008_S002_P001__llama-3.3-70b-instruct_kor.xlsx
@@ -983,6 +983,11 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1032,11 +1037,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D008_S002_P001__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D008_S002_P001__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -553,6 +554,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
